--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L219"/>
+  <dimension ref="A1:L221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-19</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>咬钩结算弹窗与自动入包</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -11891,44 +11891,44 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>上钩结束弹窗钓到/脱钩；去掉领取钮；出售档与不可回鱼只显示尺寸体重入包；回鱼档达标显示尺寸体重价格</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-19咬钩结算弹窗.md</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-ART-04</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>美术</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>橘猫钓鱼动画 Overlay 七层叠加</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11943,27 +11943,22 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>橘猫按工作台7层同帧叠加；逐帧layerOrder；baiting单独clip；无清单的猫仍走单张序列帧</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/橘猫钓鱼动画接入Overlay.md</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11970,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11985,7 +11980,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12005,7 +12000,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -12020,7 +12015,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12027,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12042,7 +12037,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12062,7 +12057,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -12077,7 +12072,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12084,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12099,7 +12094,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12119,12 +12114,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12134,7 +12129,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12141,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12156,7 +12151,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12176,7 +12171,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -12191,7 +12186,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12198,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12213,7 +12208,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12228,22 +12223,22 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12260,7 +12255,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12270,7 +12265,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12290,17 +12285,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12317,7 +12312,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12327,7 +12322,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12342,27 +12337,27 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12369,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12384,7 +12379,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12399,17 +12394,17 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12419,7 +12414,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12426,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12441,7 +12436,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12456,17 +12451,17 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12476,7 +12471,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12483,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12498,7 +12493,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12518,12 +12513,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12533,7 +12528,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12540,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12555,7 +12550,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12570,17 +12565,17 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12590,7 +12585,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12597,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12612,7 +12607,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12627,17 +12622,17 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -12647,7 +12642,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -12659,17 +12654,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12689,12 +12684,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12716,50 +12711,164 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H221" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I221" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
+      <c r="J221" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L221"/>
+  <dimension ref="A1:L242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11965,22 +11965,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>BUG-27</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>展示柜图鉴格子被纸盖住</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12000,44 +12000,44 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>个人中心大纸张画在格子和相册上面；纸张改到最底层</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>BUG-28</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>个人中心右侧米色方块溢出</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -12057,44 +12057,44 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>旧节点 Reflow_DetailPaper 仍激活，伸出窗口；已隐藏</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>BUG-29</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>图鉴标题与解锁文案重叠</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12114,44 +12114,44 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>Detail 铺满整块，标题叠在已解锁文案上；标题与正文拆开</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>BUG-30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>相册照片溢出成白条</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -12171,44 +12171,44 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>Photo 写死 613 宽，超出约 508 的槽位；改为跟随槽位</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>BUG-31</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>设置页错位且没有背景</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -12228,44 +12228,44 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>设置根 ScrollRect 背景被清掉且尺寸未统一；恢复底板并隐藏旧侧栏</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>BUG-32</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>商店装备详情压住购买按钮</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -12285,44 +12285,44 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>长说明固定高度压到按钮；改到按钮上方的独立滚动区</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>BUG-33</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>重复 Apply 清掉图集子图 ID</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12332,54 +12332,54 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>ImportAtlas 每次重写子图 ID；已切好的图集直接跳过</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>BUG-34</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>背包列表不能滚动</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -12399,44 +12399,44 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>Viewport 有两个 Slots，ScrollRect 指到空节点；改为指向装鱼获的那个</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>BUG-35</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>圆体字体把标题整行截掉</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -12456,22 +12456,22 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>Resource Han Rounded 首行过高；改行高并按 OFL 改名为 Fish Cozy Rounded</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -12483,17 +12483,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>BUG-36</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>主按钮左侧白点</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -12513,22 +12513,22 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>icons-light 金币等浅色图标破损；按亮度重做挖空</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -12540,17 +12540,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>BUG-37</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>鱼获页签选中后变灰</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -12570,22 +12570,22 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>选中态要求可点击，唯一分类被禁用后变灰；选中时保持选中底板</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -12597,17 +12597,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>BUG-38</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>鱼塘选择加网格失败</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -12627,22 +12627,22 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>Cards 已有纵向布局，加网格失败并跳过后续摆放；改为纵向列表并隐藏旧侧栏</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -12654,17 +12654,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>BUG-39</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>展示柜旧鱼图标压住新插画</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12674,32 +12674,32 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>ShowcaseSlot 自带小鱼图标与裁切后的鱼图重叠；隐藏旧图标</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -12711,17 +12711,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>BUG-40</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>第二次 Apply 破坏选中态和成就徽章</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12731,32 +12731,32 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>选中按钮把悬停底板存进 Prefab；徽章层级调整盖住文字。两次 Apply 现已一致</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -12768,17 +12768,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>BUG-41</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>九宫格测试反射到错误重载</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -12788,32 +12788,32 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>OnPopulateMesh 两个重载导致 AmbiguousMatchException；测试指定 VertexHelper</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -12825,50 +12825,1242 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
+          <t>BUG-42</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>缺字段响应仍返回半解析对象</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>TryParseResponse 失败时仍带出对象；认证与大厅客户端都改为置空</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BUG-43</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Toggle 背景套不上纸</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>允许 Toggle 的 Bg 换纸，但 ApplyPaper 因父级是 Selectable 直接返回</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BUG-44</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>目录测试仍走旧 Overlay 生成</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>自定义生成已收窄到 OverlayPondLayout；测试夹具名已对齐</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>BUG-45</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>页签卡片无选中态且详情是整段</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>补选中底板、背包商店资料的图标标签数值行，以及裁切后的鱼图</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>BUG-46</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>成就列表没有当前进度</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>AchievementViewDto 只有目标和是否解锁，没有当前进度；不改 server/shared</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>BUG-47</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>展示柜点选详情仍是整段文字</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>ShowFishDetail 改为图标、标签、数值分行；空选中仍是提示句</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07A</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>桌面宠物主视图与鱼塘入口</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07B</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2D 鱼塘环境与自己的猫咪</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07C</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>同塘玩家宠物与状态同步</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07D</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>桌面宠物右键菜单</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07E</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>桌面宠物主窗口功能页签</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07F</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>桌面宠物主流程与恢复验收</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-07G</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>原生桌面宠物 Overlay</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08A</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>世界地图与鱼塘选择</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08B</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>商店与装备</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08C</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>动态墙与好友动态</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08D</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>排行榜</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08E</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>个人中心与资料编辑</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H242" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I242" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr">
+      <c r="J242" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="K242" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L242"/>
+  <dimension ref="A1:L249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13162,17 +13162,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>BUG-48</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>Overlay HUD 导出写回旧九宫格边距导致回退旧布局</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -13192,22 +13192,22 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>OverlayHudExporter 写死 10/20，Overlay 要求 12/22，加载失败退回 XAML；回退提示被 state 覆盖</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -13219,17 +13219,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>BUG-49</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>Overlay HUD 布局重排</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13239,32 +13239,32 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>去掉菜单栏与打开主界面，只留右键菜单；状态卡与退出鱼塘放右下，钓鱼按钮底部居中，聊天栏左下 320 宽，Debug 只改宽度</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -13276,17 +13276,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>BUG-50</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>Overlay 聊天栏行数、折叠按钮对齐与发送后不清空</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13296,32 +13296,32 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>展开显示 10 行；折叠按钮固定底行右侧；发送结果按 commandId 回执，成功清空输入框</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -13333,17 +13333,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>BUG-51</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>Overlay Debug 菜单点击无反应</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13353,32 +13353,32 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>执行结果只写 ErrorText，被每条 state 覆盖且被弹窗遮住；命令未写日志，Unity 侧待验证</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -13390,17 +13390,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>BUG-52</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>Overlay 操作延迟与卡顿</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -13420,22 +13420,22 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>state 约 34 条/秒且每帧两次；UI 线程逐条处理并同步写 335MB 日志；需合并 state、限频发布、日志缓冲轮转</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -13447,17 +13447,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>BUG-53</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>Overlay 钓鱼操作动画反馈慢</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -13477,22 +13477,22 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>开始钓鱼/收杆/打窝/离席/强制咬钩回执 1.8～8 秒：Unity socket 读循环在主线程同步上下文，每帧只收一包；改线程池收发 + 本地预测动画 + 咬钩到期本地收线</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13529,27 +13529,27 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13591,22 +13591,22 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13648,22 +13648,22 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13700,27 +13700,27 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13757,27 +13757,27 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13814,27 +13814,27 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13871,22 +13871,22 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13990,12 +13990,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14017,54 +14017,449 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08C</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>动态墙与好友动态</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08D</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>排行榜</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08E</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>个人中心与资料编辑</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G248" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
+      <c r="I248" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J242" t="inlineStr">
+      <c r="J248" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="K248" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>BUG-54</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Unity 自己钓鱼表现权威</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>终态：自己钓鱼由 Unity 本地推进 phase/visual/actions；服务端只校验结算；Overlay 去掉猜阶段时间线（BUG-53 为过渡）</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/BUG修复-Unity自己钓鱼表现权威.md</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13504,17 +13504,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>BUG-54</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>Unity 自己钓鱼表现权威</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -13534,22 +13534,22 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>终态：自己钓鱼由 Unity 本地推进 phase/visual/actions；服务端只校验结算；Overlay 去掉猜阶段时间线（BUG-53 为过渡）</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Unity自己钓鱼表现权威.md</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13819,12 +13819,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13871,22 +13871,22 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13928,22 +13928,22 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13990,12 +13990,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14042,17 +14042,17 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14104,12 +14104,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14161,12 +14161,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14213,17 +14213,17 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14302,17 +14302,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14332,12 +14332,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14359,17 +14359,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bug 修复 / 功能优化</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14389,44 +14389,44 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>BUG-54</t>
+          <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Unity 自己钓鱼表现权威</t>
+          <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -14446,20 +14446,24 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>终态：自己钓鱼由 Unity 本地推进 phase/visual/actions；服务端只校验结算；Overlay 去掉猜阶段时间线（BUG-53 为过渡）</t>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Unity自己钓鱼表现权威.md</t>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L249"/>
+  <dimension ref="A1:L251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13561,17 +13561,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>BUG-55</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>默认头像白名单与源码不一致</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -13591,22 +13591,22 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>资料编辑保存新猫返回无效头像：server 加载的 shared/dist 仍是 2026-10-17 旧 6 只猫。启动必须跟 defaultAvatars.ts，禁止静默用过期 dist</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-默认头像目录与运行白名单不一致.md</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -13618,17 +13618,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>BUG-56</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>Overlay 换阶段卡帧与收杆重播</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -13648,22 +13648,22 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>管道已是数毫秒，但阶段切换 frame_stall 2～6 秒（贴图按真实槽位解码，预热尺寸对不上）。收杆到 seated 后再点会再播 stopping</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-Overlay阶段切换卡帧与收杆重播.md</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13819,12 +13819,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13928,22 +13928,22 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14042,27 +14042,27 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14099,17 +14099,17 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14156,17 +14156,17 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14270,17 +14270,17 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14327,17 +14327,17 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14359,17 +14359,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14416,50 +14416,164 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>Bug 修复 / 功能优化</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G251" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
+      <c r="H251" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
+      <c r="I251" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J249" t="inlineStr">
+      <c r="J251" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="K251" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L251"/>
+  <dimension ref="A1:L254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5008,7 +5008,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>C1+C7→C5→C6→C2→C3；C4不做</t>
+          <t>C1+C7→C5→C6→C2→C3；C4不做。2026-10-21 整包废弃，不再排期</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Phase2-下一迭代开发计划.md</t>
+          <t>docs/planning/specs/C-调优与状态机.md</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -5056,12 +5056,16 @@
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="K83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -5096,7 +5100,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>C6 引用，设计规格</t>
+          <t>C6 引用的设计规格。2026-10-21 废弃，不再作为交付物</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -5109,7 +5113,11 @@
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6189,7 +6197,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -6224,7 +6232,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>地图·背包商店·社交·排行榜</t>
+          <t>地图·背包商店·社交·排行榜。2026-10-21 废弃，不再迁入</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -6239,7 +6247,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8987,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9025,6 +9033,11 @@
       <c r="J153" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10459,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10492,6 +10505,11 @@
       <c r="J179" t="inlineStr">
         <is>
           <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10568,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10596,6 +10614,11 @@
       <c r="J181" t="inlineStr">
         <is>
           <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11936,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -11959,6 +11982,11 @@
       <c r="J205" t="inlineStr">
         <is>
           <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13076,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>待开发</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13058,7 +13086,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -13083,7 +13111,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>AchievementViewDto 只有目标和是否解锁，没有当前进度；不改 server/shared</t>
+          <t>从 Bug 修复改为功能，待开发。AchievementViewDto 只有目标和是否解锁，没有当前进度；不改 server/shared</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -13670,12 +13698,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-20</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13685,7 +13713,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>主窗口固定分辨率</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13695,7 +13723,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -13705,44 +13733,39 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>默认客户区1920×1080；设置只切1280×720/1600×900/1920×1080/2560×1440；不改Overlay 960×560</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-20主窗口固定分辨率.md</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>BUG-57</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面设置世界首页与装备图</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13752,32 +13775,27 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>设置字段不重叠；世界/鱼塘页外框对齐商店；首页全身猫；鱼饵钓竿按id取同一张图</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-桌面设置世界首页与装备图.md</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -13789,17 +13807,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>BUG-58</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>桌面鱼塘与设置信息</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13809,32 +13827,32 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>鱼塘中文信息与右栏详情；地图标记按类型着色；设置显示当前项并自动保存</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-桌面鱼塘与设置信息.md</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13864,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13856,7 +13874,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13876,7 +13894,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13891,7 +13909,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13921,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13913,7 +13931,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13933,12 +13951,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -13948,7 +13966,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13978,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13970,7 +13988,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13990,7 +14008,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -14005,7 +14023,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14035,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14027,7 +14045,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14042,27 +14060,27 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14092,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14084,7 +14102,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14104,17 +14122,17 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -14131,7 +14149,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14141,7 +14159,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14161,22 +14179,22 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14206,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14198,7 +14216,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14218,22 +14236,22 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -14245,7 +14263,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14255,7 +14273,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14270,17 +14288,17 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14290,7 +14308,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14320,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14312,7 +14330,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14327,17 +14345,17 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14359,7 +14377,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14369,7 +14387,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14384,17 +14402,17 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14404,7 +14422,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14434,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14426,7 +14444,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14441,17 +14459,17 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14461,7 +14479,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -14473,17 +14491,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14498,17 +14516,17 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14518,7 +14536,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14530,50 +14548,221 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Bug 修复 / 功能优化</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G254" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
+      <c r="H254" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
+      <c r="I254" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr">
+      <c r="J254" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K254" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -14768,7 +14957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15296,7 +15485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16980,7 +17169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18382,7 +18571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19006,6 +19195,21 @@
           <t>2026-07-12</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -19300,7 +19504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19572,7 +19776,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -19615,7 +19819,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -19822,6 +20026,21 @@
           <t>2026-07-14</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -20590,7 +20809,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -20766,7 +20985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21120,7 +21339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21286,7 +21505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -21837,7 +22056,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -22917,7 +23136,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L254"/>
+  <dimension ref="A1:L255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14767,6 +14767,59 @@
           <t>2026-08-18</t>
         </is>
       </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-21</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>猫咪钓鱼手账动效</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>按钮回弹、导航浮漂、切页、金币滚动、地图浮标、角落小猫、减少动效</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-21猫咪钓鱼手账动效.md</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开发计划'!$A$1:$L$135</definedName>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-21</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>猫咪钓鱼手账动效</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13884,32 +13884,32 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>正式手账UI、共享资源/选塘状态、动效与发布弹窗；Unity 347测试通过，Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-21猫咪钓鱼手账动效.md</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14035,7 +14035,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14122,12 +14122,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14179,12 +14179,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14231,22 +14231,22 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14288,22 +14288,22 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14350,12 +14350,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14377,7 +14377,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14402,17 +14402,17 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14464,12 +14464,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14521,12 +14521,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14573,17 +14573,17 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14635,12 +14635,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14662,17 +14662,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14692,12 +14692,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14749,44 +14749,44 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-21</t>
+          <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>猫咪钓鱼手账动效</t>
+          <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14796,30 +14796,34 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>按钮回弹、导航浮漂、切页、金币滚动、地图浮标、角落小猫、减少动效</t>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-21猫咪钓鱼手账动效.md</t>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>正式手账UI、共享资源/选塘状态、动效与发布弹窗；Unity 347测试通过，Windows联机/DPI待验收</t>
+          <t>10/22用户认可远端be6f2bdf逐项对齐修复版，沿用正式UI，结束JournalV2替换推进；Unity回归448/448，Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/22用户认可远端be6f2bdf逐项对齐修复版，沿用正式UI，结束JournalV2替换推进；Unity回归448/448，Windows联机/DPI待验收</t>
+          <t>10/22沿用认可版并补八类UI缺口：渐变/经验条/动态/收藏标签/社交分区/选塘地图；Unity回归468/468、守卫PASS、21状态截图；Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开发计划'!$A$1:$L$135</definedName>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L255"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13921,17 +13921,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>BUG-59</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>手账翻页标签与排行榜</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13941,32 +13941,32 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>合并相册翻页、空卡出场、右侧详情、日期地点、芯片五角星、通知底、榜单尺寸重量滚动条、动态留言</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/BUG修复-手账翻页标签与排行榜.md</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14179,12 +14179,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14236,12 +14236,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14288,22 +14288,22 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14345,22 +14345,22 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14459,17 +14459,17 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14521,12 +14521,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14578,12 +14578,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14630,17 +14630,17 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14692,12 +14692,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -14776,50 +14776,107 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>Bug修复</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G256" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
+      <c r="H256" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
+      <c r="I256" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J255" t="inlineStr">
+      <c r="J256" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
+      <c r="K256" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开发计划'!$A$1:$L$135</definedName>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/22沿用认可版并补八类UI缺口：渐变/经验条/动态/收藏标签/社交分区/选塘地图；Unity回归468/468、守卫PASS、21状态截图；Windows联机/DPI待验收</t>
+          <t>10/23按Web重写资料/编辑/分享/离塘结算；新增12项通过、全套476通过5旧检查失败、守卫PASS、24状态截图；Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开发计划'!$A$1:$L$135</definedName>
@@ -13076,7 +13076,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>从 Bug 修复改为功能，待开发。AchievementViewDto 只有目标和是否解锁，没有当前进度；不改 server/shared</t>
+          <t>profile-hub 下发 currentValue（复用 progressValue）；自己的未完成卡片显示当前/目标。解锁规则不变</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/BUG-46成就列表当前进度.md</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13698,7 +13698,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -13744,13 +13744,18 @@
       <c r="J236" t="inlineStr">
         <is>
           <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已验收</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -13796,6 +13801,11 @@
       <c r="J237" t="inlineStr">
         <is>
           <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开发计划'!$A$1:$L$135</definedName>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23按Web重写资料/编辑/分享/离塘结算；新增12项通过、全套476通过5旧检查失败、守卫PASS、24状态截图；Windows联机/DPI待验收</t>
+          <t>10/23按Web重写四页并同步工作区动效；专项111/111，全套498通过4旧检查失败；30张动效帧；Web闪回修复；Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23按Web重写四页并同步工作区动效；专项111/111，全套498通过4旧检查失败；30张动效帧；Web闪回修复；Windows联机/DPI待验收</t>
+          <t>10/23补修12页动效区域空绑定、开页/右栏及编辑两栏时序；Web7开页+2按钮实测，专项130/130，全套521通过4旧检查失败；42张正式路由动效帧；Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23补修12页动效区域空绑定、开页/右栏及编辑两栏时序；Web7开页+2按钮实测，专项130/130，全套521通过4旧检查失败；42张正式路由动效帧；Windows联机/DPI待验收</t>
+          <t>10/23补齐资料正文三组、经验条、编辑两栏与进退100ms淡出；保留12页动效绑定修复；Web7开页+2按钮及表单交互通过，专项137/137，全套528通过4旧检查失败；42张正式路由动效帧；Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23补齐资料正文三组、经验条、编辑两栏与进退100ms淡出；保留12页动效绑定修复；Web7开页+2按钮及表单交互通过，专项137/137，全套528通过4旧检查失败；42张正式路由动效帧；Windows联机/DPI待验收</t>
+          <t>10/23补保存成功240ms反馈、离塘收获分组入场/关闭、隐藏窗口结算延后播放；本轮专项60/60，Web开页及完成反馈通过；之前全套539通过4旧检查失败；48张正式路由动效帧；Windows联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -11914,7 +11914,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>上钩结束弹窗钓到/脱钩；去掉领取钮；出售档与不可回鱼只显示尺寸体重入包；回鱼档达标显示尺寸体重价格</t>
+          <t>10/23按用户要求取消Overlay单次钓获/回鱼/脱钩卡，保留自动结算入包与回鱼；关联21；双端过滤、Unity事件测试通过，Windows新EXE待验收</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23补保存成功240ms反馈、离塘收获分组入场/关闭、隐藏窗口结算延后播放；本轮专项60/60，Web开页及完成反馈通过；之前全套539通过4旧检查失败；48张正式路由动效帧；Windows联机/DPI待验收</t>
+          <t>10/23完成资料/结算反馈；追加Overlay桌面同源素材39个、120ms淡入淡出、移除状态栏与单次结果卡；本轮Python34/34、Unity5/5及完整导出通过；主界面上轮专项60/60；Windows新EXE构建/联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23完成资料/结算反馈；追加Overlay桌面同源素材39个、120ms淡入淡出、移除状态栏与单次结果卡；本轮Python34/34、Unity5/5及完整导出通过；主界面上轮专项60/60；Windows新EXE构建/联机/DPI待验收</t>
+          <t>10/23主界面/Overlay手账表现已实现；性能第一批补角色回收、路径共享引用、64MiB热缓存和尺寸预热；缓存8/8、静态39/39、生产WPF/原生测试交叉编译通过；Windows6组原生运行/性能/联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23主界面/Overlay手账表现已实现；性能第一批补角色回收、路径共享引用、64MiB热缓存和尺寸预热；缓存8/8、静态39/39、生产WPF/原生测试交叉编译通过；Windows6组原生运行/性能/联机/DPI待验收</t>
+          <t>10/23 Overlay性能两批已实现：回收/热缓存、后台分层解码与取消、增量布局/聊天、共享时钟/离屏暂停；调度10/10、缓存8/8、WPF编译通过；3处音效并行基线差异，Windows11组原生运行/性能/联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23 Overlay性能两批已实现：回收/热缓存、后台分层解码与取消、增量布局/聊天、共享时钟/离屏暂停；调度10/10、缓存8/8、WPF编译通过；3处音效并行基线差异，Windows11组原生运行/性能/联机/DPI待验收</t>
+          <t>10/23 Overlay性能三批已实现：回收/热缓存、后台动画/静态图加载、增量布局/聊天、共享时钟/离屏暂停、预制alpha/九宫格预算、遮罩复用及可选合并采样；行为24/24、静态48/48、WPF编译通过；Windows18组原生运行/性能/联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23 Overlay性能三批已实现：回收/热缓存、后台动画/静态图加载、增量布局/聊天、共享时钟/离屏暂停、预制alpha/九宫格预算、遮罩复用及可选合并采样；行为24/24、静态48/48、WPF编译通过；Windows18组原生运行/性能/联机/DPI待验收</t>
+          <t>10/23 Overlay性能三批及交互补修已实现：后台加载/缓存/共享时钟，修聊天命中/进塘闪屏/离塘结算顺序/头像缓存，删右键当前鱼塘；行为24/24、Unity专项34/34、静态48/48、WPF编译通过；Windows19组原生运行/性能/联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23 Overlay性能三批及交互补修已实现：后台加载/缓存/共享时钟，修聊天命中/进塘闪屏/离塘结算顺序/头像缓存，删右键当前鱼塘；行为24/24、Unity专项34/34、静态48/48、WPF编译通过；Windows19组原生运行/性能/联机/DPI待验收</t>
+          <t>10/23 Overlay性能三批及交互补修已实现；离塘等待Overlay退出→恢复桌面→底边栏同源动效展开结算，遮罩同步淡入；Unity最新专项75/75，既有行为24/24、静态48/48、WPF编译通过；Windows19组原生运行/性能/联机/DPI及窗口时序待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L256"/>
+  <dimension ref="A1:L266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>10/23 Overlay性能三批及交互补修已实现；离塘等待Overlay退出→恢复桌面→底边栏同源动效展开结算，遮罩同步淡入；Unity最新专项75/75，既有行为24/24、静态48/48、WPF编译通过；Windows19组原生运行/性能/联机/DPI及窗口时序待验收</t>
+          <t>10/24 背包道具去重、详情操作区及评论提示绑定修复，Unity专项17/17；保留10/23 Overlay性能与返回时序修复；Windows原生运行/视觉/联机/DPI待验收</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14891,6 +14891,548 @@
           <t>2026-08-18</t>
         </is>
       </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22A</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>咬钩读条手账风格</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>奶油纸底、暖橙矢量进度与棕色图标；原倒计时保留；Windows视觉待验收</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22B</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>鱼线鱼饵水面接触</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>按座位前沿校正浮漂／鱼及竿尖固定的鱼线长度；收杆渐退；6组数学测试通过，Windows视觉待验收</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22C</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Overlay聊天展开</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>折叠栏与开关预览按下展开，命中缓存失效；原生测试加入真实输入路由，Windows点击待验收</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22D</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Overlay动画补帧</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>仅记录：补关键动作中间帧，控制内存／解码成本</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22E</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>入塘离席猫咪位置与站起时序</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>仅记录：脚底与钓位对齐，站起结束后再离开</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22F</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>打窝循环动画</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>仅记录：起手、循环、收尾匹配服务器打窝时长</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22G</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Overlay背景场景美术迭代</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>仅记录：岸线、水面、钓位层次与风格优化，先预览后替换</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22H</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>钓鱼过程特效</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>仅记录：入水、波纹、咬钩、挣扎、收杆、脱钩反馈</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22I</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>钓鱼与UI音效迭代</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>仅记录：音色、音量、触发时机与并发控制</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-22J</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>世界地图迭代</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>仅记录：信息层级、标识、筛选详情与进入路径；先交互预览</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -13988,7 +13988,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-22A</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>咬钩读条手账风格</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14008,32 +14008,32 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>奶油纸底、暖橙矢量进度与棕色图标；原倒计时保留；Windows视觉待验收</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14045,17 +14045,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-22B</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>鱼线鱼饵水面接触</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14065,32 +14065,32 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>按座位前沿校正浮漂／鱼及竿尖固定的鱼线长度；收杆渐退；6组数学测试通过，Windows视觉待验收</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14102,17 +14102,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-22C</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>Overlay聊天展开</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -14132,22 +14132,22 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>折叠栏与开关预览按下展开，命中缓存失效；原生测试加入真实输入路由，Windows点击待验收</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-22D</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>Overlay动画补帧</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14179,32 +14179,32 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>抛竿13、收杆/空军16、打窝18个分层轨迹采样；总时长不变、复用PNG缓存；Windows原生待验收</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-22E</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>入塘离席猫咪位置与站起时序</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>脚底锚点统一；到位后坐下、站起尾帧结束再平滑离席；重复快照与重入保护；Windows视觉待验收</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-22F</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>打窝循环动画</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14293,44 +14293,44 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>100ms起手/720ms循环/280ms收尾，直到groundbaiting真实退出；网络更新与中断保护；Windows原生待验收</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-22G</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>Overlay背景场景美术迭代</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14350,44 +14350,39 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>仅记录：岸线、水面、钓位层次与风格优化，先预览后替换</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-22H</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14397,7 +14392,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>钓鱼过程特效</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14407,44 +14402,39 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>仅记录：入水、波纹、咬钩、挣扎、收杆、脱钩反馈</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-22I</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14454,7 +14444,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>钓鱼与UI音效迭代</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14464,44 +14454,39 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>仅记录：音色、音量、触发时机与并发控制</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-22J</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14511,7 +14496,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>世界地图迭代</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14521,32 +14506,27 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>仅记录：信息层级、标识、筛选详情与进入路径；先交互预览</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14538,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14568,7 +14548,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14583,27 +14563,27 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14595,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14625,7 +14605,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14640,27 +14620,27 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14652,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14682,7 +14662,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14702,22 +14682,22 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14739,7 +14719,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14759,22 +14739,22 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14786,17 +14766,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14816,17 +14796,17 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -14843,17 +14823,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14873,22 +14853,22 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14880,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22A</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -14910,7 +14890,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>咬钩读条手账风格</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14920,7 +14900,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -14930,22 +14910,22 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>奶油纸底、暖橙矢量进度与棕色图标；原倒计时保留；Windows视觉待验收</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14957,17 +14937,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22B</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>鱼线鱼饵水面接触</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14977,32 +14957,32 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>按座位前沿校正浮漂／鱼及竿尖固定的鱼线长度；收杆渐退；6组数学测试通过，Windows视觉待验收</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15014,17 +14994,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22C</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Overlay聊天展开</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15034,7 +15014,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -15044,34 +15024,34 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>折叠栏与开关预览按下展开，命中缓存失效；原生测试加入真实输入路由，Windows点击待验收</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22D</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15081,7 +15061,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Overlay动画补帧</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -15091,40 +15071,44 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>后续迭代</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>仅记录：补关键动作中间帧，控制内存／解码成本</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22E</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15134,7 +15118,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>入塘离席猫咪位置与站起时序</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15144,40 +15128,44 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>后续迭代</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>仅记录：脚底与钓位对齐，站起结束后再离开</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22F</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15187,7 +15175,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>打窝循环动画</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15197,40 +15185,44 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>后续迭代</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>仅记录：起手、循环、收尾匹配服务器打窝时长</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22G</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15240,7 +15232,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Overlay背景场景美术迭代</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15250,40 +15242,44 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>后续迭代</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>仅记录：岸线、水面、钓位层次与风格优化，先预览后替换</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22H</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15293,7 +15289,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>钓鱼过程特效</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15303,50 +15299,54 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>后续迭代</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>仅记录：入水、波纹、咬钩、挣扎、收杆、脱钩反馈</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22I</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>钓鱼与UI音效迭代</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15356,50 +15356,54 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>后续迭代</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>仅记录：音色、音量、触发时机与并发控制</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-22J</t>
+          <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>世界地图迭代</t>
+          <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15409,30 +15413,34 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>后续迭代</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>仅记录：信息层级、标识、筛选详情与进入路径；先交互预览</t>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -14189,7 +14189,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>抛竿13、收杆/空军16、打窝18个分层轨迹采样；总时长不变、复用PNG缓存；Windows原生待验收</t>
+          <t>扩展十角色14种动作轨迹采样，发力循环接缝、脚底固定微转、手持鱼保护；鱼下沉64原画单位；复用PNG/原时长；Windows待验收</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>100ms起手/720ms循环/280ms收尾，直到groundbaiting真实退出；网络更新与中断保护；Windows原生待验收</t>
+          <t>100ms起手/720ms循环/280ms收尾直到真实退出；撒料加水面补偿和渐进下落，收手不残留；Windows原生待验收</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>仅记录：音色、音量、触发时机与并发控制</t>
+          <t>已制作6场景交互试听与4种候选音色；事件去重、加载同步、音量和并发方案待确认后接入</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L266"/>
+  <dimension ref="A1:L269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14412,12 +14412,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>仅记录：入水、波纹、咬钩、挣扎、收杆、脱钩反馈</t>
+          <t>9类特效方案v1：共用事件/水面锚点、标准/简化/关闭、多人对象预算与验收；待视觉评审，未实现</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-22H钓鱼特效设计.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14464,12 +14464,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>已制作6场景交互试听与4种候选音色；事件去重、加载同步、音量和并发方案待确认后接入</t>
+          <t>声音方案v1：沿用6场景试听，补齐事件去重、真实帧同步、声部/后台提示/资源规范；待听感评审，未接入</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-22I声音体验设计.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>仅记录：信息层级、标识、筛选详情与进入路径；先交互预览</t>
+          <t>地图方案v1：三栏尺寸、真实点位/标签避让、筛选/缩放、档位费用确认与异常恢复；待交互评审，未实现</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/Steam桌面端-22J世界地图设计.md</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>STEAM-DESKTOP-22K</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>持续钓鱼呼吸</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14558,32 +14558,32 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>Unity/Overlay固定脚底有界呼吸、握竿同步及鱼线端点；Unity相关203/203、运动24/24；Windows待验收</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14595,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>STEAM-DESKTOP-22L</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14605,7 +14605,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>挂机瞌睡与触碰唤醒</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14615,32 +14615,32 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>默认30分钟，可配置；服务器持久化/直接逃鱼、本人触碰唤醒、11角色局部闭眼；服务端35/35；Windows待验收</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14652,17 +14652,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>STEAM-DESKTOP-22M</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>美术</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>狸花猫丧彪完整钓鱼动作</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14672,32 +14672,32 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>后续迭代</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>44原画/63源姿势/16钓鱼动作/74帧槽，头像与选择入口；家园仅站坐，未含行走进食翻滚蜷睡；Windows美术待验收</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14905,27 +14905,27 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14967,17 +14967,17 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15133,17 +15133,17 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15190,17 +15190,17 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15247,17 +15247,17 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -15336,17 +15336,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15361,17 +15361,17 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -15393,50 +15393,221 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
+          <t>STEAM-DESKTOP-08F</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>好友列表与申请 Prefab</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08G</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Overlay 钓鱼操作栏</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>STEAM-DESKTOP-08H</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>全量 UI 预制体化与动态内容组件</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>v1.0-steam-desktop</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C269" t="inlineStr">
         <is>
           <t>Bug修复</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G269" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H269" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
+      <c r="I269" t="inlineStr">
         <is>
           <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr">
+      <c r="J269" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="K269" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -14412,7 +14412,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>9类特效方案v1：共用事件/水面锚点、标准/简化/关闭、多人对象预算与验收；待视觉评审，未实现</t>
+          <t>资源/代码已接入：四档18纹理、11角色预览、池化Overlay及Unity兜底；本机验证已执行；Windows/I联测与视觉验收待完成，完成日期暂留空</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -14429,7 +14429,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>声音方案v1：沿用6场景试听，补齐事件去重、真实帧同步、声部/后台提示/资源规范；待听感评审，未接入</t>
+          <t>v2纸张物音/28条独立实录水声/柔音钢琴循环/九场景A-B；Unity-WPF事件去重与四声部接入，工程验证通过；Windows画声延迟和耳机/扬声器听感待验收</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -14473,6 +14473,11 @@
         </is>
       </c>
       <c r="J249" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -14412,7 +14412,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>资源/代码已接入：四档18纹理、11角色预览、池化Overlay及Unity兜底；本机验证已执行；Windows/I联测与视觉验收待完成，完成日期暂留空</t>
+          <t>v4风格已确认；按追加要求区分波纹/飞溅并修正入水落点，恢复真实收杆触水；Overlay/Unity本机验证，Windows/I实机待验收</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>v2纸张物音/28条独立实录水声/柔音钢琴循环/九场景A-B；Unity-WPF事件去重与四声部接入，工程验证通过；Windows画声延迟和耳机/扬声器听感待验收</t>
+          <t>v5配乐与46条v3音效及猫声已采用并应用；旧版音频和无效工具已清理，来源许可留档；Unity-WPF已接入，Windows画声延迟待实测</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -14377,7 +14377,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>v4风格已确认；按追加要求区分波纹/飞溅并修正入水落点，恢复真实收杆触水；Overlay/Unity本机验证，Windows/I实机待验收</t>
+          <t>用户正式采用v4造型与v8鱼塘配色；七类真实触水效果、放大波纹及三端接入完成，本机验证通过；Windows性能/点击穿透及H/I实机待验收</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -14423,6 +14423,11 @@
       <c r="J248" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -14412,7 +14412,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>用户正式采用v4造型与v8鱼塘配色；七类真实触水效果、放大波纹及三端接入完成，本机验证通过；Windows性能/点击穿透及H/I实机待验收</t>
+          <t>v4造型与v8配色已采用；2026-10-26补上钩浮漂沉浮/摆动，水花对齐当前鱼线入水点，正式随包程序已更新；Windows性能/点击穿透及H/I实机待验收</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开发计划'!$A$1:$L$135</definedName>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L269"/>
+  <dimension ref="A1:L272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14325,7 +14325,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>仅记录：岸线、水面、钓位层次与风格优化，先预览后替换</t>
+          <t>2026-10-25/26 全塘粉彩绘本布局、千岛湖分层和登录粉彩已入库；时长限制提示同批进 HUD。Windows 实机未单独验收</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -14371,6 +14371,11 @@
       <c r="J247" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14531,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>地图方案v1：三栏尺寸、真实点位/标签避让、筛选/缩放、档位费用确认与异常恢复；待交互评审，未实现</t>
+          <t>地图方案v1：三栏尺寸、点位/标签避让、筛选/缩放、档位费用确认；地理文案改由 WORLD-CAT-01 提供，本项仍未实现</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15622,6 +15627,165 @@
           <t>2026-08-18</t>
         </is>
       </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>WORLD-CAT-01</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>猫咪世界观与场景描述</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>地图和鱼塘场景不再以中国实景为叙事；保留塘 id 与鱼种表，另写猫咪世界分区和每塘场景描述</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/猫咪世界观与场景描述.md</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>FISH-ATTR-01</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>体长体重步进与公式评判</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>体长步进 0.01m 改为 0.05m，体重展示步进 0.1kg。40m/7日成长和 40m 脱钩 98.5% 判定为不适合当前尺度，本票不改系数</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/钓鱼体长体重步进与公式评判.md</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>OPS-HOT-1</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>运维</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>桌面资源与数值热更</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>不重做 OPS-RELEASE-1。准备 Overlay 资源包和钓鱼数值表的不停服替换与回滚，不热更 exe</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>docs/planning/specs/桌面资源与数值热更.md</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据平台-Phase 1+" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构修复" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug修复" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能特性" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值与生态" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排查工具" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec 文档清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开发计划'!$A$1:$L$135</definedName>
@@ -570,7 +570,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/三层数据体系-可观测性补充-v0.6.md</t>
+          <t>docs/planning/specs/data-ops/三层数据体系-可观测性补充-v0.6.md</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/埋点优化-咬钩脱钩计数替代tick.md</t>
+          <t>docs/planning/specs/data-ops/埋点优化-咬钩脱钩计数替代tick.md</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/埋点优化-相位跳转短码.md</t>
+          <t>docs/planning/specs/data-ops/埋点优化-相位跳转短码.md</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Admin-能力不足分析与补充方案.md</t>
+          <t>docs/planning/specs/data-ops/Admin-能力不足分析与补充方案.md</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Admin-排障增强-v1.2.md</t>
+          <t>docs/planning/specs/data-ops/Admin-排障增强-v1.2.md</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Admin可读化与运营入口精简.md</t>
+          <t>docs/planning/specs/data-ops/Admin可读化与运营入口精简.md</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Admin页签合并与看板图表化.md</t>
+          <t>docs/planning/specs/data-ops/Admin页签合并与看板图表化.md</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/运营增长与商业化指标看板.md</t>
+          <t>docs/planning/specs/data-ops/运营增长与商业化指标看板.md</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/看板产量人机分列-背包口径.md</t>
+          <t>docs/planning/specs/data-ops/看板产量人机分列-背包口径.md</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Admin与业务健康产量对齐背包.md</t>
+          <t>docs/planning/specs/data-ops/Admin与业务健康产量对齐背包.md</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/发版与热更策略.md</t>
+          <t>docs/planning/specs/backend/发版与热更策略.md</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/每日钓鱼时长-上海日重置.md</t>
+          <t>docs/planning/specs/gameplay/每日钓鱼时长-上海日重置.md</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/机器人账号池与清理.md</t>
+          <t>docs/planning/specs/gameplay/机器人账号池与清理.md</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/机器人进塘节奏与初始时长.md</t>
+          <t>docs/planning/specs/gameplay/机器人进塘节奏与初始时长.md</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓点手动选择.md</t>
+          <t>docs/planning/specs/gameplay/钓点手动选择.md</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/运营日报-剩余需求交接.md</t>
+          <t>docs/planning/specs/data-ops/运营日报-剩余需求交接.md</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/运营日报-剩余需求交接.md</t>
+          <t>docs/planning/specs/data-ops/运营日报-剩余需求交接.md</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/运营日报-剩余需求交接.md</t>
+          <t>docs/planning/specs/data-ops/运营日报-剩余需求交接.md</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-DP-D-BI与合规交接.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-DP-D-BI与合规交接.md</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/运营日报-剩余需求交接.md</t>
+          <t>docs/planning/specs/data-ops/运营日报-剩余需求交接.md</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/运营日报-剩余需求交接.md</t>
+          <t>docs/planning/specs/data-ops/运营日报-剩余需求交接.md</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数据平台-DP-D-BI与合规交接.md</t>
+          <t>docs/planning/specs/data-ops/数据平台-DP-D-BI与合规交接.md</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/服务器维护-端口占用.md</t>
+          <t>docs/planning/specs/backend/服务器维护-端口占用.md</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/服务器架构缺陷与埋点设计-v0.4.4.md</t>
+          <t>docs/planning/specs/data-ops/服务器架构缺陷与埋点设计-v0.4.4.md</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/架构-单实例容量与真人隔离-R2-3.md</t>
+          <t>docs/planning/specs/backend/架构-单实例容量与真人隔离-R2-3.md</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/phase2-开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/phase2-开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/phase2-开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/phase2-开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/phase2-开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/phase2-开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/A0-数值重构.md</t>
+          <t>docs/archive/2026-10-26/retired/planning/specs/A0-数值重构.md</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数值重构v2-成长咬钩与文案.md</t>
+          <t>docs/planning/specs/gameplay/数值重构v2-成长咬钩与文案.md</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数值重构-品质尺寸咬钩脱钩.md</t>
+          <t>docs/planning/specs/gameplay/数值重构-品质尺寸咬钩脱钩.md</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/生态调优-咬钩间隔与鱼群恢复.md</t>
+          <t>docs/planning/specs/gameplay/生态调优-咬钩间隔与鱼群恢复.md</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓点鱼群流动性与分区咬钩.md</t>
+          <t>docs/planning/specs/gameplay/钓点鱼群流动性与分区咬钩.md</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/咬钩产量调优-单鱼抽样与脱钩.md</t>
+          <t>docs/planning/specs/gameplay/咬钩产量调优-单鱼抽样与脱钩.md</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/A1-飘字广播.md</t>
+          <t>docs/planning/specs/gameplay/A1-飘字广播.md</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/A2-Debug面板.md</t>
+          <t>docs/planning/specs/gameplay/A2-Debug面板.md</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/B0-商店基础.md</t>
+          <t>docs/planning/specs/gameplay/B0-商店基础.md</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/B1-鱼饵偏好.md</t>
+          <t>docs/planning/specs/gameplay/B1-鱼饵偏好.md</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/C-调优与状态机.md</t>
+          <t>docs/archive/2026-10-26/retired/planning/specs/C-调优与状态机.md</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/状态机需求描述.md</t>
+          <t>docs/archive/2026-10-26/retired/planning/specs/状态机需求描述.md</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/社交互动-动态点赞.md</t>
+          <t>docs/planning/specs/gameplay/社交互动-动态点赞.md</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/社交互动-动态评论.md</t>
+          <t>docs/planning/specs/gameplay/社交互动-动态评论.md</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/排行榜系统.md</t>
+          <t>docs/planning/specs/gameplay/排行榜系统.md</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/排行榜-入口与领奖台改版.md</t>
+          <t>docs/planning/specs/gameplay/排行榜-入口与领奖台改版.md</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/鱼塘场景与社交列表UI优化.md</t>
+          <t>docs/planning/specs/world/鱼塘场景与社交列表UI优化.md</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/鱼塘叠加层与背包社交收口.md</t>
+          <t>docs/planning/specs/gameplay/鱼塘叠加层与背包社交收口.md</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/等距网格世界与鱼塘场景.md</t>
+          <t>docs/planning/specs/world/等距网格世界与鱼塘场景.md</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/等距网格世界与鱼塘场景.md</t>
+          <t>docs/planning/specs/world/等距网格世界与鱼塘场景.md</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/星露谷式正交Tilemap场景.md</t>
+          <t>docs/planning/specs/world/星露谷式正交Tilemap场景.md</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Tilemap相机拖拽与HUD分层.md</t>
+          <t>docs/planning/specs/world/Tilemap相机拖拽与HUD分层.md</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Tilemap性能与二十塘扩容.md</t>
+          <t>docs/planning/specs/world/Tilemap性能与二十塘扩容.md</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/世界地图全屏与层级缩放.md</t>
+          <t>docs/planning/specs/world/世界地图全屏与层级缩放.md</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/后端优化-问题汇总与分批计划.md</t>
+          <t>docs/planning/specs/backend/后端优化-问题汇总与分批计划.md</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/后端优化-A-安全收口.md</t>
+          <t>docs/planning/specs/backend/后端优化-A-安全收口.md</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/后端优化-B-热路径性能.md</t>
+          <t>docs/planning/specs/backend/后端优化-B-热路径性能.md</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/会话计时tick仅必要字段.md</t>
+          <t>docs/planning/specs/data-ops/会话计时tick仅必要字段.md</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/服务端日志降噪与分层输出.md</t>
+          <t>docs/planning/specs/backend/服务端日志降噪与分层输出.md</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/运营平台入口体验增强.md</t>
+          <t>docs/planning/specs/data-ops/运营平台入口体验增强.md</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/后端优化-C-停机与稳定性.md</t>
+          <t>docs/planning/specs/backend/后端优化-C-停机与稳定性.md</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/后端优化-D-工程债与部署.md</t>
+          <t>docs/planning/specs/backend/后端优化-D-工程债与部署.md</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/后端优化-E-千人多机前置.md</t>
+          <t>docs/planning/specs/backend/后端优化-E-千人多机前置.md</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/UI体验修复-社交商店图鉴.md</t>
+          <t>docs/planning/specs/gameplay/UI体验修复-社交商店图鉴.md</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/他人主页优化.md</t>
+          <t>docs/planning/specs/gameplay/他人主页优化.md</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-资料与鱼塘UI.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-资料与鱼塘UI.md</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-四项体验问题.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-四项体验问题.md</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-鱼塘钓鱼时长显示.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-鱼塘钓鱼时长显示.md</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/分析与修复-钓鱼概率与饵文案.md</t>
+          <t>docs/planning/specs/gameplay/分析与修复-钓鱼概率与饵文案.md</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-挂机断线离位.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-挂机断线离位.md</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-切页误离塘与计时中断.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-切页误离塘与计时中断.md</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-会话计时广播回归.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-会话计时广播回归.md</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/phase2-开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-演示模式与自动打开浏览器.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-演示模式与自动打开浏览器.md</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-演示模式与自动打开浏览器.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-演示模式与自动打开浏览器.md</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr"/>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-tsx-watch启动挂死.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-tsx-watch启动挂死.md</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-BI与游戏Web入口不可用.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-BI与游戏Web入口不可用.md</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-垂钓中头顶0秒闪烁.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-垂钓中头顶0秒闪烁.md</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-今日剩余时长不刷新.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-今日剩余时长不刷新.md</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-今日额度跨日不刷新.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-今日额度跨日不刷新.md</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-断线离塘未结算丢失钓鱼时长.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-断线离塘未结算丢失钓鱼时长.md</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-离塘导航失效与收杆按钮闪烁.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-离塘导航失效与收杆按钮闪烁.md</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-进塘首帧状态与演示降级.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-进塘首帧状态与演示降级.md</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/排查-挂机断线诊断阶段2-4.md</t>
+          <t>docs/planning/specs/gameplay/排查-挂机断线诊断阶段2-4.md</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-每日额度单一口径重构.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-每日额度单一口径重构.md</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-进塘与钓鱼剩余展示回归.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-进塘与钓鱼剩余展示回归.md</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端独立游戏转型计划.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端独立游戏转型计划.md</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端产品定位与信息架构.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端产品定位与信息架构.md</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam身份账号绑定与安全会话.md</t>
+          <t>docs/planning/specs/desktop/Steam身份账号绑定与安全会话.md</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam好友Lobby邀请与鱼塘映射.md</t>
+          <t>docs/planning/specs/desktop/Steam好友Lobby邀请与鱼塘映射.md</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>docs/planning/specs/空鱼塘休眠与生态离线补算.md</t>
+          <t>docs/planning/specs/gameplay/空鱼塘休眠与生态离线补算.md</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity Windows桌面端基础壳.md</t>
+          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-桌面端关闭后进程残留.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-桌面端关闭后进程残留.md</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-SteamLobby创建权限与状态残留.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-SteamLobby创建权限与状态残留.md</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam Lobby生命周期与邀请反馈优化.md</t>
+          <t>docs/archive/2026-10-26/retired/planning/specs/Steam Lobby生命周期与邀请反馈优化.md</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物UI需求拆分.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面宠物UI需求拆分.md</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面Overlay场景布局管线.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面Overlay场景布局管线.md</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-09AOverlay玩家右键菜单.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-09AOverlay玩家右键菜单.md</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-09BOverlay悬停状态与钓鱼时长.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-09BOverlay悬停状态与钓鱼时长.md</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-09COverlay鱼塘聊天气泡与输入.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-09COverlay鱼塘聊天气泡与输入.md</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-09DOverlay布局与角色表现优化.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-09DOverlay布局与角色表现优化.md</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端公网联调与服务器地址配置.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端公网联调与服务器地址配置.md</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端本机公网映射联调.md</t>
+          <t>docs/archive/2026-10-26/retired/planning/specs/Steam桌面端本机公网映射联调.md</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端云服务器联调保留.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端云服务器联调保留.md</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓鱼玩法扩展-v0.7-Epic.md</t>
+          <t>docs/planning/specs/gameplay/钓鱼玩法扩展-v0.7-Epic.md</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>docs/planning/specs/鱼塘分级与玩家成长.md</t>
+          <t>docs/planning/specs/gameplay/鱼塘分级与玩家成长.md</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓具与鱼饵配置.md</t>
+          <t>docs/planning/specs/gameplay/钓具与鱼饵配置.md</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A2世界地图分区与进塘扣费.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08A2世界地图分区与进塘扣费.md</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>docs/planning/specs/禁止钓鱼塘巡警事件.md</t>
+          <t>docs/planning/specs/gameplay/禁止钓鱼塘巡警事件.md</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓位点位线索文字泡.md</t>
+          <t>docs/planning/specs/gameplay/钓位点位线索文字泡.md</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-新手引导本地教学关.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-新手引导本地教学关.md</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-玩法Debug菜单.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-玩法Debug菜单.md</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>docs/planning/specs/回鱼机制.md</t>
+          <t>docs/planning/specs/gameplay/回鱼机制.md</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>docs/planning/specs/打窝机制.md</t>
+          <t>docs/planning/specs/gameplay/打窝机制.md</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓鱼相册与成就.md</t>
+          <t>docs/planning/specs/gameplay/钓鱼相册与成就.md</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>docs/planning/specs/双价塘与自动回鱼.md</t>
+          <t>docs/planning/specs/gameplay/双价塘与自动回鱼.md</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-日额度满后仍可开钓.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-日额度满后仍可开钓.md</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>docs/planning/specs/回鱼规则调优.md</t>
+          <t>docs/planning/specs/gameplay/回鱼规则调优.md</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>docs/planning/specs/塘生态数值表驱动.md</t>
+          <t>docs/planning/specs/gameplay/塘生态数值表驱动.md</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>docs/planning/specs/中国鱼种与区域分布.md</t>
+          <t>docs/planning/specs/gameplay/中国鱼种与区域分布.md</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓位标签与线索库-v2.md</t>
+          <t>docs/planning/specs/gameplay/钓位标签与线索库-v2.md</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓位标签地形微调.md</t>
+          <t>docs/planning/specs/gameplay/钓位标签地形微调.md</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>docs/planning/specs/线索文案策划审校.md</t>
+          <t>docs/planning/specs/gameplay/线索文案策划审校.md</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓位鱼情联动线索.md</t>
+          <t>docs/planning/specs/gameplay/钓位鱼情联动线索.md</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>docs/planning/specs/自动回鱼体验闭环.md</t>
+          <t>docs/planning/specs/gameplay/自动回鱼体验闭环.md</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-Debug鱼塘钓位查看.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-Debug鱼塘钓位查看.md</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>docs/planning/specs/回鱼体重分档.md</t>
+          <t>docs/planning/specs/gameplay/回鱼体重分档.md</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>docs/planning/specs/塘人口与品质权重调参.md</t>
+          <t>docs/planning/specs/gameplay/塘人口与品质权重调参.md</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面Overlay分塘底图与HUD同步.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面Overlay分塘底图与HUD同步.md</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-13OverlayHUD聊天栏与预制体对齐.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-13OverlayHUD聊天栏与预制体对齐.md</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-13AOverlay场景边缘半透明渐隐.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-13AOverlay场景边缘半透明渐隐.md</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-13BOverlay宠物标签右键与登录窗.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-13BOverlay宠物标签右键与登录窗.md</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-13COverlay打窝HUD收口.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-13COverlay打窝HUD收口.md</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-14Overlay透明点击穿透回归.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-14Overlay透明点击穿透回归.md</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-14AOverlay钓位座位图.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-14AOverlay钓位座位图.md</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-14BOverlay横轴场景平移.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-14BOverlay横轴场景平移.md</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-14COverlayHUD正式素材与文字对齐.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-14COverlayHUD正式素材与文字对齐.md</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-14DOverlay宠物状态图标与上钩圆环.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-14DOverlay宠物状态图标与上钩圆环.md</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-15Overlay钓鱼栏按钮时序.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-15Overlay钓鱼栏按钮时序.md</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-16Overlay窗口视口缩放.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-16Overlay窗口视口缩放.md</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-17占用座位不可顶机器人.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-17占用座位不可顶机器人.md</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Overlay形象进游戏不恢复.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Overlay形象进游戏不恢复.md</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Overlay打窝按钮剩余口数.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Overlay打窝按钮剩余口数.md</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Overlay悬停与右键菜单指针命中.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Overlay悬停与右键菜单指针命中.md</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-18Overlay悬停浮窗条数与hint定位.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-18Overlay悬停浮窗条数与hint定位.md</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-14EOverlay头顶状态图标与进度环.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-14EOverlay头顶状态图标与进度环.md</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-19咬钩结算弹窗.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-19咬钩结算弹窗.md</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>docs/planning/specs/橘猫钓鱼动画接入Overlay.md</t>
+          <t>docs/planning/specs/desktop/橘猫钓鱼动画接入Overlay.md</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG-46成就列表当前进度.md</t>
+          <t>docs/planning/specs/bugs/BUG-46成就列表当前进度.md</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Unity自己钓鱼表现权威.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Unity自己钓鱼表现权威.md</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-默认头像目录与运行白名单不一致.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-默认头像目录与运行白名单不一致.md</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-Overlay阶段切换卡帧与收杆重播.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-Overlay阶段切换卡帧与收杆重播.md</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-20主窗口固定分辨率.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-20主窗口固定分辨率.md</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-桌面设置世界首页与装备图.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-桌面设置世界首页与装备图.md</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-桌面鱼塘与设置信息.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-桌面鱼塘与设置信息.md</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-21猫咪钓鱼手账动效.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-21猫咪钓鱼手账动效.md</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-手账翻页标签与排行榜.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-手账翻页标签与排行榜.md</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22H钓鱼特效设计.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22H钓鱼特效设计.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22I声音体验设计.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22I声音体验设计.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22J世界地图设计.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22J世界地图设计.md</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14719,22 +14719,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07A</t>
+          <t>WORLD-CAT-01</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>桌面宠物主视图与鱼塘入口</t>
+          <t>猫咪世界观与场景描述</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14744,44 +14744,39 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
+          <t>地图和鱼塘场景不再以中国实景为叙事；保留塘 id 与鱼种表，另写猫咪世界分区和每塘场景描述</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/world/猫咪世界观与场景描述.md</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07B</t>
+          <t>FISH-ATTR-01</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -14791,7 +14786,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2D 鱼塘环境与自己的猫咪</t>
+          <t>体长体重步进与公式评判</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14801,54 +14796,49 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
+          <t>体长步进 0.01m 改为 0.05m，体重展示步进 0.1kg。40m/7日成长和 40m 脱钩 98.5% 判定为不适合当前尺度，本票不改系数</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/gameplay/钓鱼体长体重步进与公式评判.md</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07C</t>
+          <t>OPS-HOT-1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>运维</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>同塘玩家宠物与状态同步</t>
+          <t>桌面资源与数值热更</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14858,32 +14848,27 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>v1.0-steam-desktop</t>
+          <t>hotfix</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
+          <t>不重做 OPS-RELEASE-1。准备 Overlay 资源包和钓鱼数值表的不停服替换与回滚，不热更 exe</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/backend/桌面资源与数值热更.md</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14880,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07D</t>
+          <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -14905,7 +14890,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>桌面宠物右键菜单</t>
+          <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14925,12 +14910,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
+          <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -14940,7 +14925,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14937,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07E</t>
+          <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -14962,7 +14947,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>桌面宠物主窗口功能页签</t>
+          <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14982,12 +14967,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
+          <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端Web功能对齐设计.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -14997,7 +14982,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -15009,7 +14994,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07F</t>
+          <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15019,7 +15004,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>桌面宠物主流程与恢复验收</t>
+          <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15039,12 +15024,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
+          <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面宠物与多人鱼塘表现层.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -15054,7 +15039,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -15066,7 +15051,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-07G</t>
+          <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15076,7 +15061,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>原生桌面宠物 Overlay</t>
+          <t>桌面宠物右键菜单</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -15091,27 +15076,27 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
+          <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam原生桌面宠物Overlay.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15108,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08A</t>
+          <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15133,7 +15118,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>世界地图与鱼塘选择</t>
+          <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15153,17 +15138,17 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
+          <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端Web功能对齐设计.md</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -15180,7 +15165,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08B</t>
+          <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15190,7 +15175,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>商店与装备</t>
+          <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15210,22 +15195,22 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
+          <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08B商店与装备.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15222,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08C</t>
+          <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15247,7 +15232,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>动态墙与好友动态</t>
+          <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15267,22 +15252,22 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
+          <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08C动态墙与好友动态.md</t>
+          <t>docs/planning/specs/desktop/Steam原生桌面宠物Overlay.md</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15279,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08D</t>
+          <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15304,7 +15289,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>排行榜</t>
+          <t>世界地图与鱼塘选择</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15319,17 +15304,17 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
+          <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08D排行榜.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08A世界地图与鱼塘选择.md</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15339,7 +15324,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15336,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08E</t>
+          <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15361,7 +15346,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>个人中心与资料编辑</t>
+          <t>商店与装备</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15376,17 +15361,17 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
+          <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08E个人中心与资料编辑.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08B商店与装备.md</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15408,7 +15393,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08F</t>
+          <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15418,7 +15403,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>好友列表与申请 Prefab</t>
+          <t>动态墙与好友动态</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15433,17 +15418,17 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
+          <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08F好友列表与申请Prefab.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08C动态墙与好友动态.md</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -15453,7 +15438,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15450,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08G</t>
+          <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15475,7 +15460,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Overlay 钓鱼操作栏</t>
+          <t>排行榜</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15490,17 +15475,17 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
+          <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08D排行榜.md</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -15510,7 +15495,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -15522,17 +15507,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08H</t>
+          <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>全量 UI 预制体化与动态内容组件</t>
+          <t>个人中心与资料编辑</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15547,17 +15532,17 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
+          <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08H全量UI预制体化.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08E个人中心与资料编辑.md</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -15567,7 +15552,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -15579,17 +15564,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>STEAM-DESKTOP-08I</t>
+          <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>鱼塘退出与跨塘切换优化</t>
+          <t>好友列表与申请 Prefab</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -15609,44 +15594,44 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
+          <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08F好友列表与申请Prefab.md</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>WORLD-CAT-01</t>
+          <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>功能</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>猫咪世界观与场景描述</t>
+          <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15656,50 +15641,54 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>地图和鱼塘场景不再以中国实景为叙事；保留塘 id 与鱼种表，另写猫咪世界分区和每塘场景描述</t>
+          <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>docs/planning/specs/猫咪世界观与场景描述.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>FISH-ATTR-01</t>
+          <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>体长体重步进与公式评判</t>
+          <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -15709,50 +15698,54 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>体长步进 0.01m 改为 0.05m，体重展示步进 0.1kg。40m/7日成长和 40m 脱钩 98.5% 判定为不适合当前尺度，本票不改系数</t>
+          <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓鱼体长体重步进与公式评判.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08H全量UI预制体化.md</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>OPS-HOT-1</t>
+          <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>运维</t>
+          <t>Bug修复</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>桌面资源与数值热更</t>
+          <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -15762,30 +15755,34 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>hotfix</t>
+          <t>v1.0-steam-desktop</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>不重做 OPS-RELEASE-1。准备 Overlay 资源包和钓鱼数值表的不停服替换与回滚，不热更 exe</t>
+          <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>docs/planning/specs/桌面资源与数值热更.md</t>
+          <t>docs/planning/specs/desktop/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L135"/>
@@ -19684,7 +19681,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-资料与鱼塘UI.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-资料与鱼塘UI.md</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -19731,7 +19728,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-四项体验问题.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-四项体验问题.md</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -19778,7 +19775,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-鱼塘钓鱼时长显示.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-鱼塘钓鱼时长显示.md</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -19825,7 +19822,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/分析与修复-钓鱼概率与饵文案.md</t>
+          <t>docs/planning/specs/gameplay/分析与修复-钓鱼概率与饵文案.md</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -19872,7 +19869,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-挂机断线离位.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-挂机断线离位.md</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -19919,7 +19916,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-切页误离塘与计时中断.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-切页误离塘与计时中断.md</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -19966,7 +19963,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-会话计时广播回归.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-会话计时广播回归.md</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -20013,7 +20010,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Phase2-下一迭代开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/Phase2-下一迭代开发计划.md</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -20060,7 +20057,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-演示模式与自动打开浏览器.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-演示模式与自动打开浏览器.md</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -20107,7 +20104,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-演示模式与自动打开浏览器.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-演示模式与自动打开浏览器.md</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -20154,7 +20151,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-tsx-watch启动挂死.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-tsx-watch启动挂死.md</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -20201,7 +20198,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-BI与游戏Web入口不可用.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-BI与游戏Web入口不可用.md</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -20263,7 +20260,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-垂钓中头顶0秒闪烁.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-垂钓中头顶0秒闪烁.md</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -20310,7 +20307,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-今日剩余时长不刷新.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-今日剩余时长不刷新.md</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -20357,7 +20354,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-今日额度跨日不刷新.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-今日额度跨日不刷新.md</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -20404,7 +20401,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-断线离塘未结算丢失钓鱼时长.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-断线离塘未结算丢失钓鱼时长.md</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -20451,7 +20448,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-离塘导航失效与收杆按钮闪烁.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-离塘导航失效与收杆按钮闪烁.md</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -20498,7 +20495,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/BUG修复-进塘首帧状态与演示降级.md</t>
+          <t>docs/planning/specs/bugs/BUG修复-进塘首帧状态与演示降级.md</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -20617,7 +20614,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/A1-飘字广播.md</t>
+          <t>docs/planning/specs/gameplay/A1-飘字广播.md</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -20664,7 +20661,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/A2-Debug面板.md</t>
+          <t>docs/planning/specs/gameplay/A2-Debug面板.md</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -20711,7 +20708,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/B0-商店基础.md</t>
+          <t>docs/planning/specs/gameplay/B0-商店基础.md</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -20758,7 +20755,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/B1-鱼饵偏好.md</t>
+          <t>docs/planning/specs/gameplay/B1-鱼饵偏好.md</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -20805,7 +20802,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Phase2-下一迭代开发计划.md</t>
+          <t>docs/planning/specs/roadmaps/Phase2-下一迭代开发计划.md</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -20848,7 +20845,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/状态机需求描述.md</t>
+          <t>docs/archive/2026-10-26/retired/planning/specs/状态机需求描述.md</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -20891,7 +20888,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/社交互动-动态点赞.md</t>
+          <t>docs/planning/specs/gameplay/社交互动-动态点赞.md</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -20938,7 +20935,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/社交互动-动态评论.md</t>
+          <t>docs/planning/specs/gameplay/社交互动-动态评论.md</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -20985,7 +20982,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/排行榜系统.md</t>
+          <t>docs/planning/specs/gameplay/排行榜系统.md</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -21032,7 +21029,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/排行榜-入口与领奖台改版.md</t>
+          <t>docs/planning/specs/gameplay/排行榜-入口与领奖台改版.md</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -21094,7 +21091,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/鱼塘场景与社交列表UI优化.md</t>
+          <t>docs/planning/specs/world/鱼塘场景与社交列表UI优化.md</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -21141,7 +21138,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/鱼塘叠加层与背包社交收口.md</t>
+          <t>docs/planning/specs/gameplay/鱼塘叠加层与背包社交收口.md</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -21188,7 +21185,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓点手动选择.md</t>
+          <t>docs/planning/specs/gameplay/钓点手动选择.md</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -21235,7 +21232,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/等距网格世界与鱼塘场景.md</t>
+          <t>docs/planning/specs/world/等距网格世界与鱼塘场景.md</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -21282,7 +21279,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/等距网格世界与鱼塘场景.md</t>
+          <t>docs/planning/specs/world/等距网格世界与鱼塘场景.md</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -21329,7 +21326,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/星露谷式正交Tilemap场景.md</t>
+          <t>docs/planning/specs/world/星露谷式正交Tilemap场景.md</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -21376,7 +21373,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Tilemap相机拖拽与HUD分层.md</t>
+          <t>docs/planning/specs/world/Tilemap相机拖拽与HUD分层.md</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -21423,7 +21420,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Tilemap性能与二十塘扩容.md</t>
+          <t>docs/planning/specs/world/Tilemap性能与二十塘扩容.md</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -21470,7 +21467,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/世界地图全屏与层级缩放.md</t>
+          <t>docs/planning/specs/world/世界地图全屏与层级缩放.md</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -21603,7 +21600,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -21697,7 +21694,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -21744,7 +21741,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -21791,7 +21788,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -21838,7 +21835,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -21885,7 +21882,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/Unity移植-分阶段需求清单.md</t>
+          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -21932,7 +21929,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/UI体验修复-社交商店图鉴.md</t>
+          <t>docs/planning/specs/gameplay/UI体验修复-社交商店图鉴.md</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -21979,7 +21976,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/他人主页优化.md</t>
+          <t>docs/planning/specs/gameplay/他人主页优化.md</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -22098,7 +22095,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/A0-数值重构.md</t>
+          <t>docs/archive/2026-10-26/retired/planning/specs/A0-数值重构.md</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -22145,7 +22142,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数值重构v2-成长咬钩与文案.md</t>
+          <t>docs/planning/specs/gameplay/数值重构v2-成长咬钩与文案.md</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -22192,7 +22189,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/数值重构-品质尺寸咬钩脱钩.md</t>
+          <t>docs/planning/specs/gameplay/数值重构-品质尺寸咬钩脱钩.md</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -22239,7 +22236,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/生态调优-咬钩间隔与鱼群恢复.md</t>
+          <t>docs/planning/specs/gameplay/生态调优-咬钩间隔与鱼群恢复.md</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -22286,7 +22283,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/钓点鱼群流动性与分区咬钩.md</t>
+          <t>docs/planning/specs/gameplay/钓点鱼群流动性与分区咬钩.md</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -22333,7 +22330,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/咬钩产量调优-单鱼抽样与脱钩.md</t>
+          <t>docs/planning/specs/gameplay/咬钩产量调优-单鱼抽样与脱钩.md</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -22452,7 +22449,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/排查-挂机断线诊断阶段2-4.md</t>
+          <t>docs/planning/specs/gameplay/排查-挂机断线诊断阶段2-4.md</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -22499,7 +22496,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/三层数据体系-可观测性补充-v0.6.md</t>
+          <t>docs/planning/specs/data-ops/三层数据体系-可观测性补充-v0.6.md</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -14474,7 +14474,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>钓鱼场景关闭BGM与按钮音，新增水声/风声/树叶三轨独立ASMR循环与2秒淡入淡出；独立混音并接入预览，保留动作声/猫叫；Windows画声延迟待实测</t>
+          <t>钓鱼场景关闭BGM与按钮音，平静/轻晃湖面按塘配置，采用总页连续交融风叶，共享风势与衔接循环；交叉淡化与独立试听，保留动作声/猫叫；Windows画声延迟待实测</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Unity/Overlay固定脚底有界呼吸、握竿同步及鱼线端点；Unity相关203/203、运动24/24；Windows待验收</t>
+          <t>10/30按确认预览将呼吸提升至清醒±2.2%/睡着±2.8%，Unity/Overlay固定脚底、握竿及线端；Unity187/187、Overlay7/7；总预览#rest；Windows待验收</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14645,7 +14645,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>默认30分钟，可配置；服务器持久化/直接逃鱼、本人触碰唤醒、11角色局部闭眼；服务端35/35；Windows待验收</t>
+          <t>10/30新增6.4秒八阶段低头/停顿/抬头，Unity/Overlay连续形变；保留默认30分钟与服务器权威唤醒/脱钩；统一总预览#rest；Windows待验收</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/docs/planning/项目开发需求计划表.xlsx
+++ b/docs/planning/项目开发需求计划表.xlsx
@@ -14474,7 +14474,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>钓鱼场景关闭BGM与按钮音，平静/轻晃湖面按塘配置，采用总页连续交融风叶，共享风势与衔接循环；交叉淡化与独立试听，保留动作声/猫叫；Windows画声延迟待实测</t>
+          <t>钓鱼场景关闭BGM与按钮音，分塘湖面与连续交融风叶已采用；保留动作声/猫叫；10月31日首页原创BGM《晴窗小憩》候选加入总页，待试听采用，正式v5暂保留；Windows画声延迟待实测</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
